--- a/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,7; 90,29</t>
+          <t>47,16; 92,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 89,93</t>
+          <t>29,3; 90,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 77,96</t>
+          <t>11,14; 85,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,26; 92,1</t>
+          <t>51,35; 91,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,88; 93,88</t>
+          <t>52,19; 93,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,41; 90,6</t>
+          <t>34,67; 90,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,62; 72,7</t>
+          <t>17,44; 73,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,61; 80,21</t>
+          <t>33,58; 80,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,09; 87,56</t>
+          <t>58,83; 88,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 82,35</t>
+          <t>39,19; 81,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 66,76</t>
+          <t>22,65; 66,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,33; 81,27</t>
+          <t>51,98; 80,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,71; 91,73</t>
+          <t>35,38; 91,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,01; 92,75</t>
+          <t>40,15; 92,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,19</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,68; 100,0</t>
+          <t>54,01; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,26; 100,0</t>
+          <t>56,26; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 85,07</t>
+          <t>30,99; 84,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 76,54</t>
+          <t>22,46; 76,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,21; 92,01</t>
+          <t>46,24; 92,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,48; 92,59</t>
+          <t>57,72; 92,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,19; 84,63</t>
+          <t>46,16; 84,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 70,79</t>
+          <t>23,16; 70,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,79; 91,01</t>
+          <t>59,23; 90,89</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,08; 100,0</t>
+          <t>32,7; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,73; 91,16</t>
+          <t>36,62; 91,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,93; 100,0</t>
+          <t>36,92; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,06; 89,68</t>
+          <t>47,82; 89,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,8; 84,62</t>
+          <t>38,61; 86,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 78,19</t>
+          <t>10,84; 76,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,41; 93,63</t>
+          <t>38,08; 94,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,32; 90,7</t>
+          <t>55,09; 91,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,27; 80,5</t>
+          <t>46,85; 82,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,51; 82,32</t>
+          <t>30,67; 81,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,52; 95,46</t>
+          <t>46,72; 95,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,69; 83,54</t>
+          <t>46,13; 83,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,01; 78,59</t>
+          <t>52,16; 77,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,59; 74,42</t>
+          <t>35,83; 74,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,76; 91,76</t>
+          <t>60,31; 92,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,68; 84,25</t>
+          <t>51,6; 84,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,85; 69,76</t>
+          <t>41,67; 69,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,98; 100,0</t>
+          <t>71,65; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,07; 77,44</t>
+          <t>46,87; 77,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,42; 80,02</t>
+          <t>55,59; 79,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,79; 69,82</t>
+          <t>49,91; 70,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,33; 84,49</t>
+          <t>56,87; 82,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,16; 81,38</t>
+          <t>56,32; 82,65</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 85,34</t>
+          <t>29,54; 84,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,88; 85,86</t>
+          <t>47,5; 83,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,4; 78,83</t>
+          <t>34,74; 78,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,18; 82,41</t>
+          <t>37,28; 82,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,89; 75,0</t>
+          <t>35,3; 74,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,29; 82,12</t>
+          <t>50,16; 83,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,32; 74,65</t>
+          <t>17,68; 72,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,96; 97,67</t>
+          <t>61,38; 97,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,68; 74,31</t>
+          <t>41,7; 72,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,65; 79,91</t>
+          <t>55,29; 78,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,32; 70,55</t>
+          <t>34,37; 69,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,36; 91,06</t>
+          <t>59,58; 91,42</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,38; 100,0</t>
+          <t>23,48; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,92</t>
+          <t>0,0; 74,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 91,83</t>
+          <t>0,0; 71,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,03; 100,0</t>
+          <t>9,2; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,4; 72,66</t>
+          <t>17,41; 72,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,84; 92,88</t>
+          <t>38,24; 92,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,94; 79,52</t>
+          <t>19,7; 80,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,61; 79,04</t>
+          <t>10,14; 76,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,2; 74,9</t>
+          <t>27,23; 76,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,49; 77,03</t>
+          <t>29,61; 75,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 70,09</t>
+          <t>18,05; 68,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 73,7</t>
+          <t>23,52; 76,63</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,47; 77,7</t>
+          <t>57,19; 77,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,89; 73,38</t>
+          <t>55,74; 72,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,24; 65,72</t>
+          <t>41,48; 65,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,67</t>
+          <t>65,19; 84,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,47; 75,69</t>
+          <t>59,6; 76,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,31; 69,55</t>
+          <t>53,58; 69,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,76; 68,31</t>
+          <t>45,0; 68,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,33; 79,38</t>
+          <t>59,16; 79,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,0; 75,02</t>
+          <t>61,63; 75,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,02; 68,92</t>
+          <t>57,42; 69,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,12; 63,27</t>
+          <t>47,03; 65,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,74; 78,98</t>
+          <t>64,26; 79,14</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7313</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2297</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8732</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4752</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16047</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8941</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4617; 9026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1993; 6139</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>597; 4555</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5455; 9737</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5988; 10747</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2598; 6791</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1304; 5461</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4791; 11415</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12509; 18763</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5603; 11618</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2907; 8521</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12938; 20107</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6420</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7518</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8352</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12824</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11341</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15346</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2726; 7048</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3402; 7849</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2567</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4429; 8201</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4887; 8687</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2574; 7045</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1916; 6495</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5198; 10415</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9462; 15225</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7746; 14142</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2571; 7858</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>11516; 17673</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5376</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2779</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9702</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>12860</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13188</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1256; 3842</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2997; 7458</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1227; 3323</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6312; 11860</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4690; 10446</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>623; 4418</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2958; 7315</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9387; 15580</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9523; 16865</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2781; 7407</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4826; 9825</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11118</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9229</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19735</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14181</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10365</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19722</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25299</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>42405</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>39457</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7635; 13776</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17645; 26357</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5880; 12283</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15110; 23067</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10332; 16865</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14914; 24877</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7848; 10953</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>14636; 24096</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20332; 28977</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>34746; 48733</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15561; 22693</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>31699; 46517</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11813</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8129</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8163</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8856</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16055</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>22159</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14209</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>27868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12727</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>30321</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2584; 7355</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8250; 14419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4777; 10778</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4854; 10693</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5475; 11584</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11845; 19611</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1752; 7215</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16265; 25822</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10115; 17696</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>22660; 32332</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8132; 16536</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>23543; 36126</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1086; 4626</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3687</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2064</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>376; 4089</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1268; 5253</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2432; 5908</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1409; 5726</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>572; 4316</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3243; 9090</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3344; 8568</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1813; 6913</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2288; 7455</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>35098</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>51553</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>23761</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>52213</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>58160</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>28687</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>66559</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>87310</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>109713</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>52448</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>114684</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>29318; 39745</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>44366; 57778</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18379; 29162</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>41428; 53707</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>45398; 58402</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>50214; 65406</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>22395; 34320</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>57168; 76871</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>78541; 96347</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>99514; 120685</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>44242; 61265</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>102937; 126768</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,16; 92,21</t>
+          <t>48,19; 93,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,3; 90,25</t>
+          <t>29,84; 89,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 85,01</t>
+          <t>10,15; 77,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,35; 91,66</t>
+          <t>55,19; 92,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,19; 93,66</t>
+          <t>52,25; 93,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,67; 90,62</t>
+          <t>34,39; 90,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 73,05</t>
+          <t>16,81; 72,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,58; 80,03</t>
+          <t>36,31; 79,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,83; 88,24</t>
+          <t>57,88; 87,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,19; 81,26</t>
+          <t>41,24; 82,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 66,4</t>
+          <t>21,3; 66,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 80,79</t>
+          <t>50,28; 81,08</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,38; 91,49</t>
+          <t>34,98; 91,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,15; 92,62</t>
+          <t>44,24; 92,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,01; 100,0</t>
+          <t>54,76; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,26; 100,0</t>
+          <t>62,15; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 84,83</t>
+          <t>31,38; 84,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,46; 76,13</t>
+          <t>28,34; 82,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 92,65</t>
+          <t>45,89; 92,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,72; 92,88</t>
+          <t>56,9; 91,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,16; 84,28</t>
+          <t>45,18; 83,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,16; 70,81</t>
+          <t>23,34; 71,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,23; 90,89</t>
+          <t>59,49; 91,39</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,7; 100,0</t>
+          <t>30,63; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 91,15</t>
+          <t>38,15; 91,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,92; 100,0</t>
+          <t>27,22; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,82; 89,86</t>
+          <t>48,22; 89,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,61; 86,01</t>
+          <t>40,92; 84,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 76,92</t>
+          <t>11,02; 77,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,08; 94,17</t>
+          <t>38,69; 93,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,09; 91,43</t>
+          <t>54,53; 88,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,85; 82,97</t>
+          <t>46,54; 82,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,67; 81,69</t>
+          <t>29,69; 80,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,72; 95,12</t>
+          <t>49,7; 95,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,13; 83,23</t>
+          <t>46,98; 83,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,16; 77,91</t>
+          <t>51,59; 78,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,83; 74,84</t>
+          <t>34,48; 73,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,31; 92,06</t>
+          <t>61,37; 92,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,6; 84,22</t>
+          <t>53,42; 84,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,67; 69,5</t>
+          <t>42,19; 69,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,65; 100,0</t>
+          <t>76,49; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,87; 77,16</t>
+          <t>46,87; 77,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,59; 79,22</t>
+          <t>55,39; 81,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,91; 70,0</t>
+          <t>51,27; 69,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,87; 82,93</t>
+          <t>56,51; 83,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,32; 82,65</t>
+          <t>56,41; 80,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,54; 84,07</t>
+          <t>28,18; 84,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,5; 83,02</t>
+          <t>47,86; 83,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,74; 78,39</t>
+          <t>36,29; 78,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,28; 82,13</t>
+          <t>37,79; 82,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,3; 74,7</t>
+          <t>35,65; 75,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,16; 83,05</t>
+          <t>51,26; 82,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 72,81</t>
+          <t>21,19; 72,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,38; 97,46</t>
+          <t>60,6; 97,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41,7; 72,95</t>
+          <t>42,62; 73,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,29; 78,89</t>
+          <t>55,32; 79,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 69,9</t>
+          <t>35,41; 70,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,58; 91,42</t>
+          <t>58,31; 91,42</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,48; 100,0</t>
+          <t>25,4; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,71</t>
+          <t>0,0; 73,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 100,0</t>
+          <t>17,78; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,41; 72,11</t>
+          <t>17,28; 72,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,24; 92,88</t>
+          <t>38,23; 92,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 80,08</t>
+          <t>19,23; 79,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 76,52</t>
+          <t>10,44; 77,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,23; 76,32</t>
+          <t>26,75; 74,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,61; 75,84</t>
+          <t>28,93; 76,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 68,82</t>
+          <t>14,9; 69,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,52; 76,63</t>
+          <t>22,15; 75,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,19; 77,53</t>
+          <t>57,6; 80,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,74; 72,59</t>
+          <t>56,01; 73,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,48; 65,82</t>
+          <t>42,25; 65,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65,19; 84,51</t>
+          <t>65,62; 84,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,6; 76,67</t>
+          <t>58,9; 76,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,58; 69,79</t>
+          <t>53,83; 71,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,0; 68,96</t>
+          <t>46,37; 68,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,16; 79,54</t>
+          <t>58,63; 79,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,63; 75,6</t>
+          <t>61,75; 75,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,42; 69,64</t>
+          <t>57,53; 69,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,03; 65,13</t>
+          <t>47,07; 63,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,26; 79,14</t>
+          <t>64,52; 79,21</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4617; 9026</t>
+          <t>4718; 9168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1993; 6139</t>
+          <t>2030; 6118</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>597; 4555</t>
+          <t>544; 4163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5455; 9737</t>
+          <t>5863; 9845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5988; 10747</t>
+          <t>5995; 10758</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2598; 6791</t>
+          <t>2577; 6812</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1304; 5461</t>
+          <t>1257; 5444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4791; 11415</t>
+          <t>5180; 11389</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12509; 18763</t>
+          <t>12307; 18592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5603; 11618</t>
+          <t>5896; 11735</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2907; 8521</t>
+          <t>2734; 8517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12938; 20107</t>
+          <t>12513; 20178</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2726; 7048</t>
+          <t>2694; 7048</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3402; 7849</t>
+          <t>3750; 7849</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4429; 8201</t>
+          <t>4491; 8201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4887; 8687</t>
+          <t>5399; 8687</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2574; 7045</t>
+          <t>2606; 7011</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1916; 6495</t>
+          <t>2418; 7067</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5198; 10415</t>
+          <t>5159; 10437</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9462; 15225</t>
+          <t>9327; 15079</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7746; 14142</t>
+          <t>7581; 13975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2571; 7858</t>
+          <t>2590; 7915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11516; 17673</t>
+          <t>11568; 17770</t>
         </is>
       </c>
     </row>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1256; 3842</t>
+          <t>1177; 3842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2997; 7458</t>
+          <t>3121; 7456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1227; 3323</t>
+          <t>905; 3323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6312; 11860</t>
+          <t>6364; 11844</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4690; 10446</t>
+          <t>4970; 10262</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>623; 4418</t>
+          <t>633; 4453</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2958; 7315</t>
+          <t>3005; 7294</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9387; 15580</t>
+          <t>9292; 15114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9523; 16865</t>
+          <t>9461; 16687</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2781; 7407</t>
+          <t>2692; 7326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4826; 9825</t>
+          <t>5133; 9874</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7635; 13776</t>
+          <t>7777; 13838</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17645; 26357</t>
+          <t>17452; 26405</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5880; 12283</t>
+          <t>5659; 12055</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15110; 23067</t>
+          <t>15376; 23239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10332; 16865</t>
+          <t>10697; 16865</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14914; 24877</t>
+          <t>15103; 24780</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7848; 10953</t>
+          <t>8378; 10953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14636; 24096</t>
+          <t>14635; 24282</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20332; 28977</t>
+          <t>20260; 29730</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34746; 48733</t>
+          <t>35696; 48554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15561; 22693</t>
+          <t>15464; 22786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31699; 46517</t>
+          <t>31749; 45260</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2584; 7355</t>
+          <t>2465; 7417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8250; 14419</t>
+          <t>8312; 14417</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4777; 10778</t>
+          <t>4989; 10850</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4854; 10693</t>
+          <t>4921; 10745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5475; 11584</t>
+          <t>5528; 11646</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11845; 19611</t>
+          <t>12104; 19568</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1752; 7215</t>
+          <t>2099; 7209</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16265; 25822</t>
+          <t>16056; 25712</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10115; 17696</t>
+          <t>10338; 17933</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22660; 32332</t>
+          <t>22670; 32375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8132; 16536</t>
+          <t>8377; 16668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23543; 36126</t>
+          <t>23041; 36126</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1086; 4626</t>
+          <t>1175; 4626</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 3640</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>376; 4089</t>
+          <t>727; 4089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1268; 5253</t>
+          <t>1258; 5273</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2432; 5908</t>
+          <t>2432; 5909</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1409; 5726</t>
+          <t>1375; 5679</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>572; 4316</t>
+          <t>589; 4347</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3243; 9090</t>
+          <t>3186; 8890</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3344; 8568</t>
+          <t>3268; 8605</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1813; 6913</t>
+          <t>1497; 6950</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2288; 7455</t>
+          <t>2154; 7324</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29318; 39745</t>
+          <t>29528; 41171</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44366; 57778</t>
+          <t>44582; 58356</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18379; 29162</t>
+          <t>18720; 28970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41428; 53707</t>
+          <t>41701; 53764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45398; 58402</t>
+          <t>44867; 58258</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50214; 65406</t>
+          <t>50449; 66877</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22395; 34320</t>
+          <t>23076; 34293</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57168; 76871</t>
+          <t>56660; 76458</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78541; 96347</t>
+          <t>78698; 95685</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99514; 120685</t>
+          <t>99710; 120259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44242; 61265</t>
+          <t>44275; 60163</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>102937; 126768</t>
+          <t>103352; 126891</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61,49%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>74,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>61,59%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>42,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>77,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,19; 93,66</t>
+          <t>51,88; 93,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,84; 89,94</t>
+          <t>30,41; 90,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 77,69</t>
+          <t>17,62; 72,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,19; 92,68</t>
+          <t>36,49; 81,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,25; 93,76</t>
+          <t>42,7; 90,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,39; 90,9</t>
+          <t>30,36; 89,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 72,82</t>
+          <t>9,63; 77,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 79,85</t>
+          <t>51,55; 91,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,88; 87,44</t>
+          <t>57,09; 87,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,24; 82,08</t>
+          <t>40,01; 82,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 66,36</t>
+          <t>22,67; 66,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,28; 81,08</t>
+          <t>52,8; 83,14</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>52,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>68,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>75,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>28,19%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>85,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>52,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,98; 91,49</t>
+          <t>62,26; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,24; 92,61</t>
+          <t>26,25; 85,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>22,03; 76,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,76; 100,0</t>
+          <t>44,35; 91,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,15; 100,0</t>
+          <t>31,71; 91,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 84,42</t>
+          <t>45,01; 92,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 82,84</t>
+          <t>0,0; 79,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 92,84</t>
+          <t>53,03; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,9; 91,99</t>
+          <t>56,48; 92,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,18; 83,29</t>
+          <t>48,19; 84,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,34; 71,32</t>
+          <t>23,47; 70,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,49; 91,39</t>
+          <t>58,09; 90,76</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64,32%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>82,21%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>65,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>83,63%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70,66%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75,47%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,63; 100,0</t>
+          <t>49,06; 89,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 91,12</t>
+          <t>38,8; 84,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,22; 100,0</t>
+          <t>11,0; 78,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>32,47; 94,08</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29,08; 100,0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>37,73; 91,16</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22,93; 100,0</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>48,22; 89,74</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>40,92; 84,5</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,02; 77,52</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38,69; 93,9</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,53; 88,7</t>
+          <t>54,32; 90,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,54; 82,09</t>
+          <t>46,27; 80,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 80,79</t>
+          <t>28,51; 82,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,7; 95,59</t>
+          <t>44,99; 95,99</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66,33%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>67,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>65,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>56,23%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,98; 83,6</t>
+          <t>53,68; 84,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,59; 78,06</t>
+          <t>41,85; 69,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,48; 73,45</t>
+          <t>76,98; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,37; 92,75</t>
+          <t>49,5; 80,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,42; 84,22</t>
+          <t>46,69; 83,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 69,23</t>
+          <t>52,01; 78,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,49; 100,0</t>
+          <t>35,59; 74,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,87; 77,76</t>
+          <t>50,89; 86,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,39; 81,28</t>
+          <t>56,42; 80,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 69,74</t>
+          <t>49,79; 69,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,51; 83,27</t>
+          <t>57,33; 84,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,41; 80,42</t>
+          <t>56,11; 78,36</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67,99%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>61,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>59,13%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>57,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,18; 84,77</t>
+          <t>34,89; 75,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,86; 83,01</t>
+          <t>49,29; 82,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,29; 78,91</t>
+          <t>22,32; 74,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,79; 82,53</t>
+          <t>59,99; 96,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,65; 75,09</t>
+          <t>35,99; 85,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,26; 82,86</t>
+          <t>48,88; 85,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,19; 72,75</t>
+          <t>34,4; 78,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,6; 97,04</t>
+          <t>35,72; 81,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,62; 73,92</t>
+          <t>42,68; 74,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,32; 79,0</t>
+          <t>55,65; 79,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,41; 70,45</t>
+          <t>37,32; 70,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,31; 91,42</t>
+          <t>57,26; 89,35</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70,3%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42,48%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>61,58%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>30,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20,86%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,4; 100,0</t>
+          <t>17,4; 72,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,77</t>
+          <t>36,84; 92,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,31</t>
+          <t>18,94; 79,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 100,0</t>
+          <t>11,41; 80,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,28; 72,39</t>
+          <t>25,38; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,23; 92,9</t>
+          <t>0,0; 74,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 79,43</t>
+          <t>0,0; 91,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,44; 77,08</t>
+          <t>17,31; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 74,65</t>
+          <t>27,2; 74,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 76,17</t>
+          <t>27,49; 77,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,9; 69,18</t>
+          <t>18,39; 70,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 75,28</t>
+          <t>23,42; 77,02</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68,54%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62,06%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57,65%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69,7%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>68,46%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>64,77%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>53,63%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,6; 80,31</t>
+          <t>58,47; 75,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,01; 73,32</t>
+          <t>53,31; 69,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42,25; 65,39</t>
+          <t>45,76; 68,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65,62; 84,6</t>
+          <t>58,84; 79,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,9; 76,48</t>
+          <t>57,47; 77,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,83; 71,36</t>
+          <t>55,89; 73,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,37; 68,91</t>
+          <t>41,24; 65,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,63; 79,12</t>
+          <t>63,28; 81,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,75; 75,08</t>
+          <t>61,0; 75,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,53; 69,39</t>
+          <t>57,02; 68,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,07; 63,96</t>
+          <t>47,12; 63,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,52; 79,21</t>
+          <t>63,3; 78,19</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8732</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4752</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7313</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4190</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2297</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8732</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16252</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4718; 9168</t>
+          <t>5953; 10772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2030; 6118</t>
+          <t>2279; 6789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>544; 4163</t>
+          <t>1317; 5435</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5863; 9845</t>
+          <t>4673; 10459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5995; 10758</t>
+          <t>4180; 8838</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2577; 6812</t>
+          <t>2065; 6117</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1257; 5444</t>
+          <t>516; 4177</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5180; 11389</t>
+          <t>5551; 9876</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12307; 18592</t>
+          <t>12140; 18618</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5896; 11735</t>
+          <t>5720; 11772</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2734; 8517</t>
+          <t>2910; 8568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12513; 20178</t>
+          <t>12448; 19602</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7518</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8013</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5306</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6420</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>724</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7518</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4920</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4473</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15196</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2694; 7048</t>
+          <t>5409; 8687</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3750; 7849</t>
+          <t>2180; 7065</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2567</t>
+          <t>1879; 6530</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4491; 8201</t>
+          <t>4807; 9922</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5399; 8687</t>
+          <t>2443; 7067</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2606; 7011</t>
+          <t>3815; 7861</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2418; 7067</t>
+          <t>0; 2033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5159; 10437</t>
+          <t>4487; 8460</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9327; 15079</t>
+          <t>9258; 15177</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7581; 13975</t>
+          <t>8086; 14201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2590; 7915</t>
+          <t>2605; 7856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11568; 17770</t>
+          <t>11211; 17517</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9702</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5376</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2779</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9702</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7811</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2488</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7162</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1177; 3842</t>
+          <t>6475; 11836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3121; 7456</t>
+          <t>4712; 10277</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>905; 3323</t>
+          <t>632; 4491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>2187; 6336</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1117; 3842</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3087; 7459</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>762; 3323</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6364; 11844</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4970; 10262</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>633; 4453</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3005; 7294</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9292; 15114</t>
+          <t>9256; 15456</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9461; 16687</t>
+          <t>9406; 16364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2692; 7326</t>
+          <t>2585; 7464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5133; 9874</t>
+          <t>4106; 8762</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14181</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10365</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18480</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22255</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9229</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19735</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14181</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20150</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10365</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19722</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>33050</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7777; 13838</t>
+          <t>10748; 16871</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17452; 26405</t>
+          <t>14980; 24970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5659; 12055</t>
+          <t>8432; 10953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15376; 23239</t>
+          <t>13791; 22309</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10697; 16865</t>
+          <t>7728; 13829</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15103; 24780</t>
+          <t>17593; 26585</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8378; 10953</t>
+          <t>5841; 12214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14635; 24282</t>
+          <t>10300; 17414</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20260; 29730</t>
+          <t>20636; 29270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35696; 48554</t>
+          <t>34666; 48613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15464; 22786</t>
+          <t>15689; 23122</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31749; 45260</t>
+          <t>26990; 37692</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8856</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16055</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18928</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5352</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>11813</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>8129</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8163</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8856</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16055</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4598</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>26728</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2465; 7417</t>
+          <t>5411; 11630</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8312; 14417</t>
+          <t>11640; 19391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4989; 10850</t>
+          <t>2212; 7397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4921; 10745</t>
+          <t>13731; 22180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5528; 11646</t>
+          <t>3149; 7466</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12104; 19568</t>
+          <t>8489; 14912</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2099; 7209</t>
+          <t>4730; 10839</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16056; 25712</t>
+          <t>4565; 10420</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10338; 17933</t>
+          <t>10352; 18027</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22670; 32375</t>
+          <t>22807; 32750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8377; 16668</t>
+          <t>8828; 16691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23041; 36126</t>
+          <t>20425; 31869</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2369</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2849</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5183</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1175; 4626</t>
+          <t>1268; 5293</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3640</t>
+          <t>2343; 5908</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>1355; 5686</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>727; 4089</t>
+          <t>636; 4493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1258; 5273</t>
+          <t>1174; 4626</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2432; 5909</t>
+          <t>0; 3698</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1375; 5679</t>
+          <t>0; 2659</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>589; 4347</t>
+          <t>769; 4440</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3186; 8890</t>
+          <t>3239; 8920</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3268; 8605</t>
+          <t>3106; 8702</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1497; 6950</t>
+          <t>1848; 7041</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2154; 7324</t>
+          <t>2346; 7714</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>52213</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58160</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>28687</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>60432</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>35098</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>51553</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>23761</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>52213</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>58160</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>28687</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>103571</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29528; 41171</t>
+          <t>44543; 57657</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44582; 58356</t>
+          <t>49958; 65178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18720; 28970</t>
+          <t>22773; 33995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41701; 53764</t>
+          <t>51017; 68809</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44867; 58258</t>
+          <t>29460; 39835</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50449; 66877</t>
+          <t>44481; 58400</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23076; 34293</t>
+          <t>18269; 29116</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56660; 76458</t>
+          <t>37389; 48108</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78698; 95685</t>
+          <t>77742; 95606</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99710; 120259</t>
+          <t>98813; 119441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44275; 60163</t>
+          <t>44328; 59516</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>103352; 126891</t>
+          <t>92277; 113988</t>
         </is>
       </c>
     </row>
